--- a/Odsustva - SBEH _test.xlsx
+++ b/Odsustva - SBEH _test.xlsx
@@ -1,27 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sbehrs-my.sharepoint.com/personal/aleksandar_jankovic_sbeh_rs/Documents/Desktop/Workfolder-MrYankovich/Razno/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="180" documentId="11_3FBB152E94819E4354E735C8ACCC0B2DAC76966A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{374B1A48-9431-4F3C-AB80-E52524EA3CC5}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="11_3FBB152E94819E4354E735C8ACCC0B2DAC76966A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{091EE8CA-F8DF-49E8-A44E-72DC2FCC995F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-12480" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pravila" sheetId="1" r:id="rId1"/>
-    <sheet name="Uputstvo" sheetId="2" r:id="rId2"/>
-    <sheet name="Zaposleni" sheetId="3" r:id="rId3"/>
-    <sheet name="Tipovi odsustva" sheetId="4" r:id="rId4"/>
-    <sheet name="Praznici" sheetId="5" r:id="rId5"/>
-    <sheet name="Odsustva" sheetId="6" r:id="rId6"/>
-    <sheet name="Statistika" sheetId="7" r:id="rId7"/>
-    <sheet name="GO_Saldo" sheetId="8" r:id="rId8"/>
-    <sheet name="GO_Saldo_Detaljno" sheetId="9" r:id="rId9"/>
+    <sheet name="Test Test" sheetId="10" r:id="rId2"/>
+    <sheet name="Uputstvo" sheetId="2" r:id="rId3"/>
+    <sheet name="Zaposleni" sheetId="3" r:id="rId4"/>
+    <sheet name="Tipovi odsustva" sheetId="4" r:id="rId5"/>
+    <sheet name="Praznici" sheetId="5" r:id="rId6"/>
+    <sheet name="Odsustva" sheetId="6" r:id="rId7"/>
+    <sheet name="Statistika" sheetId="7" r:id="rId8"/>
+    <sheet name="GO_Saldo" sheetId="8" r:id="rId9"/>
+    <sheet name="GO_Saldo_Detaljno" sheetId="9" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="ListaAktivnih">Zaposleni!$I$2</definedName>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="192">
   <si>
     <t>Parametar</t>
   </si>
@@ -639,6 +640,9 @@
   </si>
   <si>
     <t>Liste</t>
+  </si>
+  <si>
+    <t>Test</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1312,1008 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:L26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="12" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B1" s="14">
+        <v>2026</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E1" s="18">
+        <f>DATE($B$1,MONTH(Pravila!$B$3),DAY(Pravila!$B$3))</f>
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="14">
+        <f ca="1">TODAY()</f>
+        <v>46140</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2" s="14">
+        <f>Pravila!$B$2</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="44.1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="10" t="str" cm="1">
+        <f t="array" ref="A5:A21">_xlfn.ANCHORARRAY(Zaposleni!I2)</f>
+        <v>Aleksandar Janković</v>
+      </c>
+      <c r="B5" s="10">
+        <f>IF($A5="","", _xlfn.XLOOKUP($A5, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>2</v>
+      </c>
+      <c r="C5" s="10">
+        <f>IF($A5="","", _xlfn.XLOOKUP($A5, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D5" s="10">
+        <f t="shared" ref="D5:D21" si="0">MIN(B5,$E$2)</f>
+        <v>2</v>
+      </c>
+      <c r="E5" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A5,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A5,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="10">
+        <f t="shared" ref="F5:F21" si="1">MAX(0,D5-E5)</f>
+        <v>2</v>
+      </c>
+      <c r="G5" s="10">
+        <f t="shared" ref="G5:G21" ca="1" si="2">IF($B$2&gt;$E$1,F5,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" ref="H5:H21" ca="1" si="3">C5+IF($B$2&lt;=$E$1,F5,0)</f>
+        <v>22</v>
+      </c>
+      <c r="I5" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A5,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A5,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A5,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A5,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="10">
+        <f t="shared" ref="K5:K21" ca="1" si="4">H5-I5</f>
+        <v>22</v>
+      </c>
+      <c r="L5" s="10">
+        <f t="shared" ref="L5:L21" ca="1" si="5">K5-J5</f>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="str">
+        <v>Dejan Đorić</v>
+      </c>
+      <c r="B6" s="10">
+        <f>IF($A6="","", _xlfn.XLOOKUP($A6, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>14</v>
+      </c>
+      <c r="C6" s="10">
+        <f>IF($A6="","", _xlfn.XLOOKUP($A6, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D6" s="10">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="E6" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A6,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A6,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+      <c r="G6" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>34</v>
+      </c>
+      <c r="I6" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A6,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A6,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A6,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A6,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K6" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>34</v>
+      </c>
+      <c r="L6" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="10" t="str">
+        <v>Dragan Babić</v>
+      </c>
+      <c r="B7" s="10">
+        <f>IF($A7="","", _xlfn.XLOOKUP($A7, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>10</v>
+      </c>
+      <c r="C7" s="10">
+        <f>IF($A7="","", _xlfn.XLOOKUP($A7, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D7" s="10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E7" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A7,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A7,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="G7" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="I7" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A7,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A7,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A7,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A7,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="L7" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="10" t="str">
+        <v>Ivana Rosić</v>
+      </c>
+      <c r="B8" s="10">
+        <f>IF($A8="","", _xlfn.XLOOKUP($A8, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>7</v>
+      </c>
+      <c r="C8" s="10">
+        <f>IF($A8="","", _xlfn.XLOOKUP($A8, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D8" s="10">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="E8" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A8,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A8,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="I8" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A8,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A8,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A8,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A8,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K8" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="L8" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="10" t="str">
+        <v>Luka Kostov Drndarski</v>
+      </c>
+      <c r="B9" s="10">
+        <f>IF($A9="","", _xlfn.XLOOKUP($A9, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>10</v>
+      </c>
+      <c r="C9" s="10">
+        <f>IF($A9="","", _xlfn.XLOOKUP($A9, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D9" s="10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E9" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A9,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A9,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="10">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="I9" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A9,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A9,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A9,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A9,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K9" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="L9" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="str">
+        <v>Luka Pandurov</v>
+      </c>
+      <c r="B10" s="10">
+        <f>IF($A10="","", _xlfn.XLOOKUP($A10, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>15</v>
+      </c>
+      <c r="C10" s="10">
+        <f>IF($A10="","", _xlfn.XLOOKUP($A10, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D10" s="10">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E10" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A10,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A10,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>5</v>
+      </c>
+      <c r="F10" s="10">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="G10" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="I10" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A10,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A10,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>5</v>
+      </c>
+      <c r="J10" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A10,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A10,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K10" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="L10" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="str">
+        <v>Maja Petrović</v>
+      </c>
+      <c r="B11" s="10">
+        <f>IF($A11="","", _xlfn.XLOOKUP($A11, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>16</v>
+      </c>
+      <c r="C11" s="10">
+        <f>IF($A11="","", _xlfn.XLOOKUP($A11, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D11" s="10">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E11" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A11,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A11,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="G11" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H11" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="I11" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A11,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A11,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A11,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A11,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>36</v>
+      </c>
+      <c r="L11" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="10" t="str">
+        <v>Mihailo Savić</v>
+      </c>
+      <c r="B12" s="10">
+        <f>IF($A12="","", _xlfn.XLOOKUP($A12, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>10</v>
+      </c>
+      <c r="C12" s="10">
+        <f>IF($A12="","", _xlfn.XLOOKUP($A12, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D12" s="10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E12" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A12,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A12,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="10">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="G12" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="I12" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A12,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A12,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A12,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A12,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="L12" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="str">
+        <v>Milica Milisavljević</v>
+      </c>
+      <c r="B13" s="10">
+        <f>IF($A13="","", _xlfn.XLOOKUP($A13, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>18</v>
+      </c>
+      <c r="C13" s="10">
+        <f>IF($A13="","", _xlfn.XLOOKUP($A13, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D13" s="10">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="E13" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A13,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A13,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="10">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="G13" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>38</v>
+      </c>
+      <c r="I13" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A13,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A13,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A13,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A13,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>38</v>
+      </c>
+      <c r="L13" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="str">
+        <v>Mina Simonović</v>
+      </c>
+      <c r="B14" s="10">
+        <f>IF($A14="","", _xlfn.XLOOKUP($A14, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="10">
+        <f>IF($A14="","", _xlfn.XLOOKUP($A14, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D14" s="10">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="E14" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A14,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A14,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F14" s="10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="G14" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="I14" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A14,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A14,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A14,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A14,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>25</v>
+      </c>
+      <c r="L14" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="str">
+        <v>Nikola Lazarević</v>
+      </c>
+      <c r="B15" s="10">
+        <f>IF($A15="","", _xlfn.XLOOKUP($A15, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>13</v>
+      </c>
+      <c r="C15" s="10">
+        <f>IF($A15="","", _xlfn.XLOOKUP($A15, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D15" s="10">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="E15" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A15,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A15,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="10">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="G15" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="I15" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A15,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A15,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A15,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A15,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>33</v>
+      </c>
+      <c r="L15" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="str">
+        <v>Olga Jovanović</v>
+      </c>
+      <c r="B16" s="10">
+        <f>IF($A16="","", _xlfn.XLOOKUP($A16, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>4</v>
+      </c>
+      <c r="C16" s="10">
+        <f>IF($A16="","", _xlfn.XLOOKUP($A16, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D16" s="10">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="E16" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A16,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A16,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="10">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G16" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="I16" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A16,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A16,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A16,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A16,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>24</v>
+      </c>
+      <c r="L16" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="str">
+        <v>Ružica Pantović</v>
+      </c>
+      <c r="B17" s="10">
+        <f>IF($A17="","", _xlfn.XLOOKUP($A17, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>16</v>
+      </c>
+      <c r="C17" s="10">
+        <f>IF($A17="","", _xlfn.XLOOKUP($A17, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D17" s="10">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E17" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A17,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A17,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="10">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="G17" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="I17" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A17,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A17,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A17,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A17,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>36</v>
+      </c>
+      <c r="L17" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="str">
+        <v>Slavko Marjanović</v>
+      </c>
+      <c r="B18" s="10">
+        <f>IF($A18="","", _xlfn.XLOOKUP($A18, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>16</v>
+      </c>
+      <c r="C18" s="10">
+        <f>IF($A18="","", _xlfn.XLOOKUP($A18, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D18" s="10">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="E18" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A18,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A18,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>4</v>
+      </c>
+      <c r="F18" s="10">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G18" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="I18" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A18,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A18,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>4</v>
+      </c>
+      <c r="J18" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A18,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A18,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>28</v>
+      </c>
+      <c r="L18" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="str">
+        <v>Stefan Josimov</v>
+      </c>
+      <c r="B19" s="10">
+        <f>IF($A19="","", _xlfn.XLOOKUP($A19, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>13</v>
+      </c>
+      <c r="C19" s="10">
+        <f>IF($A19="","", _xlfn.XLOOKUP($A19, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D19" s="10">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="E19" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A19,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A19,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="F19" s="10">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="G19" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>33</v>
+      </c>
+      <c r="I19" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A19,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A19,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A19,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A19,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>33</v>
+      </c>
+      <c r="L19" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="str">
+        <v>Stevo Ljubičić</v>
+      </c>
+      <c r="B20" s="10">
+        <f>IF($A20="","", _xlfn.XLOOKUP($A20, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>6</v>
+      </c>
+      <c r="C20" s="10">
+        <f>IF($A20="","", _xlfn.XLOOKUP($A20, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D20" s="10">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="E20" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A20,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A20,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>6</v>
+      </c>
+      <c r="F20" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G20" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="I20" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A20,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A20,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>2</v>
+      </c>
+      <c r="J20" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A20,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A20,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>4</v>
+      </c>
+      <c r="K20" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>18</v>
+      </c>
+      <c r="L20" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" t="str">
+        <v>Uroš Velinovski</v>
+      </c>
+      <c r="B21" s="10">
+        <f>IF($A21="","", _xlfn.XLOOKUP($A21, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
+        <v>14</v>
+      </c>
+      <c r="C21" s="10">
+        <f>IF($A21="","", _xlfn.XLOOKUP($A21, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v>20</v>
+      </c>
+      <c r="D21" s="10">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="E21" s="10">
+        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A21,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A21,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>2</v>
+      </c>
+      <c r="F21" s="10">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="G21" s="10">
+        <f t="shared" ca="1" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="10">
+        <f t="shared" ca="1" si="3"/>
+        <v>32</v>
+      </c>
+      <c r="I21" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A21,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A21,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
+        <v>2</v>
+      </c>
+      <c r="J21" s="10">
+        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A21,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A21,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="10">
+        <f t="shared" ca="1" si="4"/>
+        <v>30</v>
+      </c>
+      <c r="L21" s="10">
+        <f t="shared" ca="1" si="5"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B22" s="10"/>
+      <c r="C22" s="10" t="str">
+        <f>IF($A22="","", _xlfn.XLOOKUP($A22, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
+        <v/>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="K26" s="10"/>
+    </row>
+  </sheetData>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="whole" sqref="B1" xr:uid="{00000000-0002-0000-0800-000000000000}">
+      <formula1>2020</formula1>
+      <formula2>2035</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1CE8104-0F4D-44F1-8909-097ADC2252C6}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A49"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1525,7 +2530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2133,7 +3138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2247,7 +3252,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2424,7 +3429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:O501"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -8496,7 +9501,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9131,7 +10136,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:E21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -9519,15 +10524,15 @@
       </c>
       <c r="C20" s="26">
         <f ca="1">IFERROR(GO_Saldo_Detaljno!I20+ GO_Saldo_Detaljno!J20,"")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D20" s="26">
         <f ca="1">GO_Saldo_Detaljno!L20</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E20" s="21" t="str">
         <f ca="1">IFERROR("Isk:"&amp;TEXT(GO_Saldo_Detaljno!I20,"0.##")&amp;" | Plan:"&amp;TEXT(GO_Saldo_Detaljno!J20,"0.##"),"")</f>
-        <v>Isk:0 | Plan:04</v>
+        <v>Isk:02 | Plan:04</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -9559,987 +10564,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="12" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="B1" s="14">
-        <v>2026</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="E1" s="18">
-        <f>DATE($B$1,MONTH(Pravila!$B$3),DAY(Pravila!$B$3))</f>
-        <v>46203</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="B2" s="14">
-        <f ca="1">TODAY()</f>
-        <v>46072</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2" s="14">
-        <f>Pravila!$B$2</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="44.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="L4" s="9" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="str" cm="1">
-        <f t="array" ref="A5:A21">_xlfn.ANCHORARRAY(Zaposleni!I2)</f>
-        <v>Aleksandar Janković</v>
-      </c>
-      <c r="B5" s="10">
-        <f>IF($A5="","", _xlfn.XLOOKUP($A5, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>2</v>
-      </c>
-      <c r="C5" s="10">
-        <f>IF($A5="","", _xlfn.XLOOKUP($A5, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D5" s="10">
-        <f t="shared" ref="D5:D21" si="0">MIN(B5,$E$2)</f>
-        <v>2</v>
-      </c>
-      <c r="E5" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A5,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A5,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F5" s="10">
-        <f t="shared" ref="F5:F21" si="1">MAX(0,D5-E5)</f>
-        <v>2</v>
-      </c>
-      <c r="G5" s="10">
-        <f t="shared" ref="G5:G21" ca="1" si="2">IF($B$2&gt;$E$1,F5,0)</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="10">
-        <f t="shared" ref="H5:H21" ca="1" si="3">C5+IF($B$2&lt;=$E$1,F5,0)</f>
-        <v>22</v>
-      </c>
-      <c r="I5" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A5,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A5,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J5" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A5,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A5,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="10">
-        <f t="shared" ref="K5:K21" ca="1" si="4">H5-I5</f>
-        <v>22</v>
-      </c>
-      <c r="L5" s="10">
-        <f t="shared" ref="L5:L21" ca="1" si="5">K5-J5</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="str">
-        <v>Dejan Đorić</v>
-      </c>
-      <c r="B6" s="10">
-        <f>IF($A6="","", _xlfn.XLOOKUP($A6, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>14</v>
-      </c>
-      <c r="C6" s="10">
-        <f>IF($A6="","", _xlfn.XLOOKUP($A6, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D6" s="10">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="E6" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A6,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A6,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F6" s="10">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="G6" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>34</v>
-      </c>
-      <c r="I6" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A6,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A6,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A6,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A6,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K6" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>34</v>
-      </c>
-      <c r="L6" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="str">
-        <v>Dragan Babić</v>
-      </c>
-      <c r="B7" s="10">
-        <f>IF($A7="","", _xlfn.XLOOKUP($A7, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>10</v>
-      </c>
-      <c r="C7" s="10">
-        <f>IF($A7="","", _xlfn.XLOOKUP($A7, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D7" s="10">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E7" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A7,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A7,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="10">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="G7" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>30</v>
-      </c>
-      <c r="I7" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A7,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A7,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J7" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A7,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A7,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K7" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>30</v>
-      </c>
-      <c r="L7" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="str">
-        <v>Ivana Rosić</v>
-      </c>
-      <c r="B8" s="10">
-        <f>IF($A8="","", _xlfn.XLOOKUP($A8, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>7</v>
-      </c>
-      <c r="C8" s="10">
-        <f>IF($A8="","", _xlfn.XLOOKUP($A8, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D8" s="10">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="E8" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A8,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A8,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="10">
-        <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-      <c r="G8" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>27</v>
-      </c>
-      <c r="I8" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A8,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A8,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J8" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A8,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A8,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K8" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>27</v>
-      </c>
-      <c r="L8" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="str">
-        <v>Luka Kostov Drndarski</v>
-      </c>
-      <c r="B9" s="10">
-        <f>IF($A9="","", _xlfn.XLOOKUP($A9, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>10</v>
-      </c>
-      <c r="C9" s="10">
-        <f>IF($A9="","", _xlfn.XLOOKUP($A9, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D9" s="10">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E9" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A9,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A9,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="10">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="G9" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H9" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>30</v>
-      </c>
-      <c r="I9" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A9,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A9,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J9" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A9,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A9,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K9" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>30</v>
-      </c>
-      <c r="L9" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="str">
-        <v>Luka Pandurov</v>
-      </c>
-      <c r="B10" s="10">
-        <f>IF($A10="","", _xlfn.XLOOKUP($A10, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>15</v>
-      </c>
-      <c r="C10" s="10">
-        <f>IF($A10="","", _xlfn.XLOOKUP($A10, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D10" s="10">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="E10" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A10,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A10,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>5</v>
-      </c>
-      <c r="F10" s="10">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="G10" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>30</v>
-      </c>
-      <c r="I10" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A10,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A10,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>5</v>
-      </c>
-      <c r="J10" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A10,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A10,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K10" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>25</v>
-      </c>
-      <c r="L10" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="str">
-        <v>Maja Petrović</v>
-      </c>
-      <c r="B11" s="10">
-        <f>IF($A11="","", _xlfn.XLOOKUP($A11, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>16</v>
-      </c>
-      <c r="C11" s="10">
-        <f>IF($A11="","", _xlfn.XLOOKUP($A11, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D11" s="10">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="E11" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A11,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A11,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="10">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="G11" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H11" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>36</v>
-      </c>
-      <c r="I11" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A11,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A11,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J11" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A11,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A11,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K11" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>36</v>
-      </c>
-      <c r="L11" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="str">
-        <v>Mihailo Savić</v>
-      </c>
-      <c r="B12" s="10">
-        <f>IF($A12="","", _xlfn.XLOOKUP($A12, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>10</v>
-      </c>
-      <c r="C12" s="10">
-        <f>IF($A12="","", _xlfn.XLOOKUP($A12, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D12" s="10">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E12" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A12,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A12,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="10">
-        <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-      <c r="G12" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>30</v>
-      </c>
-      <c r="I12" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A12,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A12,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J12" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A12,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A12,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>30</v>
-      </c>
-      <c r="L12" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="str">
-        <v>Milica Milisavljević</v>
-      </c>
-      <c r="B13" s="10">
-        <f>IF($A13="","", _xlfn.XLOOKUP($A13, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>18</v>
-      </c>
-      <c r="C13" s="10">
-        <f>IF($A13="","", _xlfn.XLOOKUP($A13, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D13" s="10">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="E13" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A13,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A13,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="10">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="G13" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H13" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>38</v>
-      </c>
-      <c r="I13" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A13,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A13,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J13" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A13,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A13,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>38</v>
-      </c>
-      <c r="L13" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="str">
-        <v>Mina Simonović</v>
-      </c>
-      <c r="B14" s="10">
-        <f>IF($A14="","", _xlfn.XLOOKUP($A14, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>5</v>
-      </c>
-      <c r="C14" s="10">
-        <f>IF($A14="","", _xlfn.XLOOKUP($A14, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D14" s="10">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="E14" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A14,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A14,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F14" s="10">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="G14" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H14" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>25</v>
-      </c>
-      <c r="I14" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A14,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A14,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A14,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A14,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>25</v>
-      </c>
-      <c r="L14" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="str">
-        <v>Nikola Lazarević</v>
-      </c>
-      <c r="B15" s="10">
-        <f>IF($A15="","", _xlfn.XLOOKUP($A15, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>13</v>
-      </c>
-      <c r="C15" s="10">
-        <f>IF($A15="","", _xlfn.XLOOKUP($A15, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D15" s="10">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="E15" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A15,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A15,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F15" s="10">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="G15" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H15" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>33</v>
-      </c>
-      <c r="I15" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A15,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A15,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J15" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A15,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A15,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>33</v>
-      </c>
-      <c r="L15" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="str">
-        <v>Olga Jovanović</v>
-      </c>
-      <c r="B16" s="10">
-        <f>IF($A16="","", _xlfn.XLOOKUP($A16, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>4</v>
-      </c>
-      <c r="C16" s="10">
-        <f>IF($A16="","", _xlfn.XLOOKUP($A16, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D16" s="10">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="E16" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A16,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A16,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="10">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="G16" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H16" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>24</v>
-      </c>
-      <c r="I16" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A16,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A16,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A16,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A16,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>24</v>
-      </c>
-      <c r="L16" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="str">
-        <v>Ružica Pantović</v>
-      </c>
-      <c r="B17" s="10">
-        <f>IF($A17="","", _xlfn.XLOOKUP($A17, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>16</v>
-      </c>
-      <c r="C17" s="10">
-        <f>IF($A17="","", _xlfn.XLOOKUP($A17, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D17" s="10">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="E17" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A17,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A17,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="10">
-        <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-      <c r="G17" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H17" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>36</v>
-      </c>
-      <c r="I17" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A17,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A17,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A17,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A17,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>36</v>
-      </c>
-      <c r="L17" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="str">
-        <v>Slavko Marjanović</v>
-      </c>
-      <c r="B18" s="10">
-        <f>IF($A18="","", _xlfn.XLOOKUP($A18, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>16</v>
-      </c>
-      <c r="C18" s="10">
-        <f>IF($A18="","", _xlfn.XLOOKUP($A18, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D18" s="10">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="E18" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A18,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A18,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>4</v>
-      </c>
-      <c r="F18" s="10">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="G18" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>32</v>
-      </c>
-      <c r="I18" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A18,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A18,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>4</v>
-      </c>
-      <c r="J18" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A18,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A18,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>28</v>
-      </c>
-      <c r="L18" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="str">
-        <v>Stefan Josimov</v>
-      </c>
-      <c r="B19" s="10">
-        <f>IF($A19="","", _xlfn.XLOOKUP($A19, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>13</v>
-      </c>
-      <c r="C19" s="10">
-        <f>IF($A19="","", _xlfn.XLOOKUP($A19, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D19" s="10">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="E19" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A19,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A19,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="F19" s="10">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="G19" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>33</v>
-      </c>
-      <c r="I19" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A19,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A19,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J19" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A19,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A19,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>33</v>
-      </c>
-      <c r="L19" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="str">
-        <v>Stevo Ljubičić</v>
-      </c>
-      <c r="B20" s="10">
-        <f>IF($A20="","", _xlfn.XLOOKUP($A20, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>6</v>
-      </c>
-      <c r="C20" s="10">
-        <f>IF($A20="","", _xlfn.XLOOKUP($A20, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D20" s="10">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="E20" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A20,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A20,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>6</v>
-      </c>
-      <c r="F20" s="10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="G20" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H20" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>20</v>
-      </c>
-      <c r="I20" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A20,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A20,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A20,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A20,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>4</v>
-      </c>
-      <c r="K20" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>20</v>
-      </c>
-      <c r="L20" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" t="str">
-        <v>Uroš Velinovski</v>
-      </c>
-      <c r="B21" s="10">
-        <f>IF($A21="","", _xlfn.XLOOKUP($A21, Zaposleni!$B$2:$B$200, Zaposleni!$G$2:$G$200, ""))</f>
-        <v>14</v>
-      </c>
-      <c r="C21" s="10">
-        <f>IF($A21="","", _xlfn.XLOOKUP($A21, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v>20</v>
-      </c>
-      <c r="D21" s="10">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="E21" s="10">
-        <f>SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A21,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A21,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$E$1,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>2</v>
-      </c>
-      <c r="F21" s="10">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="G21" s="10">
-        <f t="shared" ca="1" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H21" s="10">
-        <f t="shared" ca="1" si="3"/>
-        <v>32</v>
-      </c>
-      <c r="I21" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A21,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A21,Odsustva!$G$2:$G$500,$B$1,Odsustva!$E$2:$E$500,"&lt;="&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Evidentirano")</f>
-        <v>2</v>
-      </c>
-      <c r="J21" s="10">
-        <f ca="1">SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A21,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Planirano")+SUMIFS(Odsustva!$F$2:$F$500,Odsustva!$B$2:$B$500,$A21,Odsustva!$G$2:$G$500,$B$1,Odsustva!$D$2:$D$500,"&gt;"&amp;$B$2,Odsustva!$K$2:$K$500,"DA",Odsustva!$J$2:$J$500,"Odobreno")</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="10">
-        <f t="shared" ca="1" si="4"/>
-        <v>30</v>
-      </c>
-      <c r="L21" s="10">
-        <f t="shared" ca="1" si="5"/>
-        <v>30</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B22" s="10"/>
-      <c r="C22" s="10" t="str">
-        <f>IF($A22="","", _xlfn.XLOOKUP($A22, Zaposleni!$B$2:$B$200, Zaposleni!$H$2:$H$200, ""))</f>
-        <v/>
-      </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10"/>
-      <c r="L25" s="10"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="K26" s="10"/>
-    </row>
-  </sheetData>
-  <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="whole" sqref="B1" xr:uid="{00000000-0002-0000-0800-000000000000}">
-      <formula1>2020</formula1>
-      <formula2>2035</formula2>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>